--- a/Side Bar Files/GWD Data/Gravel for TWC.xlsx
+++ b/Side Bar Files/GWD Data/Gravel for TWC.xlsx
@@ -316,12 +316,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -754,7 +760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC4FC9E4-3A96-4731-BE60-5CE31444B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE0992B-3A35-4127-99C8-0DB3E6E6B9A7}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Gravel for TWC.xlsx
+++ b/Side Bar Files/GWD Data/Gravel for TWC.xlsx
@@ -9,7 +9,13 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -283,25 +289,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -379,11 +371,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -462,6 +454,113 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="GWD DR Abstract"/>
+      <sheetName val="GWD MR Abstract"/>
+      <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
+      <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
+      <sheetName val="GI on Wall PRICE"/>
+      <sheetName val="GI wo Trench"/>
+      <sheetName val="GI With Trench PRICE"/>
+      <sheetName val="GI Works"/>
+      <sheetName val="Gravel for TWC"/>
+      <sheetName val="Gutter&amp;Clamp"/>
+      <sheetName val="HP Erection and Pullout"/>
+      <sheetName val="HP Repair Labour"/>
+      <sheetName val="HP Repair Spares"/>
+      <sheetName val="Hydrants"/>
+      <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
+      <sheetName val="Metallic PH"/>
+      <sheetName val="Motor Starter GWD"/>
+      <sheetName val="Motor Starter Monoblock"/>
+      <sheetName val="Motor Starter PRICE"/>
+      <sheetName val="Other Fittings PRICE"/>
+      <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
+      <sheetName val="Pump Erection "/>
+      <sheetName val="Pump Pullout"/>
+      <sheetName val="PVC Fittings"/>
+      <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
+      <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
+      <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
+      <sheetName val="PVC With Trench"/>
+      <sheetName val="Scaffolding"/>
+      <sheetName val="Services"/>
+      <sheetName val="TW Casing Pipes"/>
+      <sheetName val="UG Cable PRICE"/>
+      <sheetName val="Water Meter"/>
+      <sheetName val="Water Tank"/>
+      <sheetName val="Well Protection"/>
+      <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
+      <sheetName val="ZCost Index"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -760,7 +859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE0992B-3A35-4127-99C8-0DB3E6E6B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F3B68-F5E3-48C2-BB49-C915D3EEBAA6}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -877,11 +976,12 @@
         <v>1</v>
       </c>
       <c r="E8" s="11">
-        <v>6553.19</v>
+        <f t="array" ref="E8">IFERROR(INDEX(LMRRates,MATCH(B7,LMRCodes,0),),)</f>
+        <v>6553</v>
       </c>
       <c r="F8" s="17">
         <f>D8*E8</f>
-        <v>6553.19</v>
+        <v>6553</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>19</v>
@@ -901,7 +1001,7 @@
       </c>
       <c r="F9" s="17">
         <f>F8</f>
-        <v>6553.19</v>
+        <v>6553</v>
       </c>
       <c r="G9" s="19"/>
     </row>
@@ -919,7 +1019,7 @@
       </c>
       <c r="F10" s="20">
         <f>F9/D9</f>
-        <v>6553.19</v>
+        <v>6553</v>
       </c>
       <c r="G10" s="19"/>
     </row>
@@ -932,11 +1032,11 @@
       <c r="D11" s="4"/>
       <c r="E11" s="17">
         <f>F10</f>
-        <v>6553.19</v>
+        <v>6553</v>
       </c>
       <c r="F11" s="17">
         <f>E11*1%</f>
-        <v>65.531899999999993</v>
+        <v>65.53</v>
       </c>
       <c r="G11" s="19"/>
     </row>
@@ -950,7 +1050,7 @@
       <c r="E12" s="19"/>
       <c r="F12" s="20">
         <f>F10+F11</f>
-        <v>6618.7218999999996</v>
+        <v>6618.53</v>
       </c>
       <c r="G12" s="19"/>
     </row>
@@ -963,11 +1063,11 @@
       <c r="D13" s="4"/>
       <c r="E13" s="17">
         <f>F12</f>
-        <v>6618.7218999999996</v>
+        <v>6618.53</v>
       </c>
       <c r="F13" s="17">
         <f>E13*15%</f>
-        <v>992.80828499999996</v>
+        <v>992.77949999999998</v>
       </c>
       <c r="G13" s="19"/>
     </row>
@@ -981,7 +1081,7 @@
       <c r="E14" s="19"/>
       <c r="F14" s="20">
         <f>ROUND(F12+F13,2)</f>
-        <v>7611.53</v>
+        <v>7611.31</v>
       </c>
       <c r="G14" s="19"/>
     </row>
@@ -1257,7 +1357,7 @@
     <row r="32" spans="1:7" ht="12.75">
       <c r="A32" s="22" t="str">
         <f>CONCATENATE("Say ₹ ",F14," + ",F31," x Cost Index")</f>
-        <v>Say ₹ 7611.53 + 826.67 x Cost Index</v>
+        <v>Say ₹ 7611.31 + 826.67 x Cost Index</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>

--- a/Side Bar Files/GWD Data/Gravel for TWC.xlsx
+++ b/Side Bar Files/GWD Data/Gravel for TWC.xlsx
@@ -859,7 +859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F3B68-F5E3-48C2-BB49-C915D3EEBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9014B49-E0C0-42FA-9257-86B7940BBAA6}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Gravel for TWC.xlsx
+++ b/Side Bar Files/GWD Data/Gravel for TWC.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -504,10 +504,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -859,7 +859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9014B49-E0C0-42FA-9257-86B7940BBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065CF170-6B5E-4898-BCEF-05982126BAA6}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
